--- a/Result/profitability/6944.xlsx
+++ b/Result/profitability/6944.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM17"/>
+  <dimension ref="A1:AM18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2589,6 +2589,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6944</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5080</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3635</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F18" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1211</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>23.83%</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>23</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1234</v>
+      </c>
+      <c r="K18" t="n">
+        <v>872</v>
+      </c>
+      <c r="L18" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="M18" t="n">
+        <v>7.915000000000001</v>
+      </c>
+      <c r="N18" t="n">
+        <v>23.65875</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.1319444444444444</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.290000000000003</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.0475138121546963</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.2323943661971832</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.450000000000003</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.3549309194854695</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK18" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
